--- a/docs/進め方.xlsx
+++ b/docs/進め方.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="JWT認証とは" sheetId="2" r:id="rId2"/>
+    <sheet name="Flutterロードマップ" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="261">
   <si>
     <t>私ならこの構成を第一候補にします</t>
   </si>
@@ -774,12 +775,179 @@
   <si>
     <t>初心者のうちは、**「JWTはログイン後にもらうデジタルな身分証明書で、APIを利用するたびに提示し、サーバーはその身分証明書が本物かどうかを確認している」**とイメージすると理解しやすいでしょう。</t>
   </si>
+  <si>
+    <t>私ならこう進めます</t>
+  </si>
+  <si>
+    <t>あなたの学習目的は</t>
+  </si>
+  <si>
+    <t>Spring Boot + Flutterでチャットアプリを作ること</t>
+  </si>
+  <si>
+    <t>ですよね。</t>
+  </si>
+  <si>
+    <t>だったらまずは</t>
+  </si>
+  <si>
+    <t>Flutter(Web)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        ↓</t>
+  </si>
+  <si>
+    <t>Spring Boot</t>
+  </si>
+  <si>
+    <t>まで完成させます。</t>
+  </si>
+  <si>
+    <t>その後、</t>
+  </si>
+  <si>
+    <t>「Androidでも動かしてみよう」</t>
+  </si>
+  <si>
+    <t>という段階でAndroid Studioを入れれば十分です。</t>
+  </si>
+  <si>
+    <t>今のロードマップ</t>
+  </si>
+  <si>
+    <t>私なら次のように変更します。</t>
+  </si>
+  <si>
+    <t>✅ Spring Boot</t>
+  </si>
+  <si>
+    <t>✅ PostgreSQL</t>
+  </si>
+  <si>
+    <t>✅ REST API</t>
+  </si>
+  <si>
+    <t>✅ Flutter(Web)</t>
+  </si>
+  <si>
+    <t>GET /health</t>
+  </si>
+  <si>
+    <t>POST /users</t>
+  </si>
+  <si>
+    <t>チャット画面完成</t>
+  </si>
+  <si>
+    <t>Android Studio導入</t>
+  </si>
+  <si>
+    <t>Android実機確認</t>
+  </si>
+  <si>
+    <t>この順番なら、環境構築で時間を使いすぎず、本来の目的であるチャットアプリ開発に集中できます。</t>
+  </si>
+  <si>
+    <t>次のステップ</t>
+  </si>
+  <si>
+    <r>
+      <t>Android SDKのインストールは</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>一旦保留</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>にして、Flutterプロジェクトを作りましょう。</t>
+    </r>
+  </si>
+  <si>
+    <t>flutter create mobile</t>
+  </si>
+  <si>
+    <t>そして、</t>
+  </si>
+  <si>
+    <t>cd mobile</t>
+  </si>
+  <si>
+    <t>flutter run -d chrome</t>
+  </si>
+  <si>
+    <t>でデフォルトのFlutterアプリがChromeで起動することを確認します。</t>
+  </si>
+  <si>
+    <r>
+      <t>その後は、そのアプリから</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Spring Bootの </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>GET /health</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> を呼び出す</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ところまで一緒に進めていきましょう。これはAndroid版でもWeb版でもほぼ同じコードなので、学習効率も良いですよ。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,6 +1014,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -873,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -908,6 +1084,12 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -923,6 +1105,87 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>130045</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>68862</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="259080" y="13464540"/>
+          <a:ext cx="5829805" cy="3254022"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>175881</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>363</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="259080" y="16984980"/>
+          <a:ext cx="7171041" cy="4191363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2974,4 +3237,245 @@
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:B67"/>
+  <sheetFormatPr defaultColWidth="3.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="3.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="14"/>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B6" s="15" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B8" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B10" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B12" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B13" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B14" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B18" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="B26" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B28" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B30" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B31" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B32" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B33" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B34" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B35" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B36" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B37" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B38" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B39" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B40" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B41" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B42" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B43" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B44" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B45" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B46" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B47" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B48" s="8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" ht="21" x14ac:dyDescent="0.2">
+      <c r="B54" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B56" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B57" s="5"/>
+    </row>
+    <row r="58" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B58" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B60" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B61" s="5"/>
+    </row>
+    <row r="62" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B62" s="8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="B63" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B65" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" ht="15" x14ac:dyDescent="0.35">
+      <c r="B67" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>